--- a/input/xlsx/112.xlsx
+++ b/input/xlsx/112.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="630" yWindow="630" windowWidth="26535" windowHeight="12465" activeTab="2"/>
+    <workbookView xWindow="630" yWindow="630" windowWidth="26535" windowHeight="12465" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="Draft" sheetId="1" r:id="rId1"/>
@@ -595,13 +595,13 @@
     <t>Winner</t>
   </si>
   <si>
-    <t>12/10/2025</t>
-  </si>
-  <si>
     <t>7.0</t>
   </si>
   <si>
     <t>Ranking</t>
+  </si>
+  <si>
+    <t>11/21/2025</t>
   </si>
 </sst>
 </file>
@@ -671,7 +671,7 @@
       <alignment horizontal="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -686,6 +686,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -2792,7 +2795,7 @@
         <v>191</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
@@ -2882,15 +2885,18 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:A2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="14" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="5" t="s">
-        <v>192</v>
+      <c r="A1" s="6" t="s">
+        <v>194</v>
       </c>
     </row>
     <row r="2" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
   </sheetData>
